--- a/assurance/sim/render-tool/template.xlsx
+++ b/assurance/sim/render-tool/template.xlsx
@@ -531,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Risk-scene renderer: one row of a risk assessment in, a scene dashboard out (assurance/sim/render-tool).</t>
+          <t>Hazard Scene Studio: one row of a risk assessment in, a scene dashboard out (assurance/sim/render-tool).</t>
         </is>
       </c>
     </row>
